--- a/Result/profitability/4729.xlsx
+++ b/Result/profitability/4729.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0.11</v>
+        <v>0.1275</v>
       </c>
       <c r="N2" t="n">
-        <v>21.76375</v>
+        <v>21.89875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.47</v>
       </c>
       <c r="M3" t="n">
-        <v>0.14875</v>
+        <v>0.1625</v>
       </c>
       <c r="N3" t="n">
-        <v>22.495</v>
+        <v>22.23375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.98</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2475</v>
+        <v>0.27125</v>
       </c>
       <c r="N4" t="n">
-        <v>22.615</v>
+        <v>22.515</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.27</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2</v>
+        <v>0.24375</v>
       </c>
       <c r="N5" t="n">
-        <v>21.73625</v>
+        <v>21.71625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05624999999999999</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>19.71</v>
+        <v>20.15625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-2.38</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.25</v>
+        <v>-0.2175</v>
       </c>
       <c r="N7" t="n">
-        <v>16.71875</v>
+        <v>16.7075</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.325</v>
+        <v>-0.2925</v>
       </c>
       <c r="N8" t="n">
-        <v>15.93125</v>
+        <v>15.405</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-1.18</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4775</v>
+        <v>-0.4774999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>14.32375</v>
@@ -1645,7 +1645,7 @@
         <v>-0.08</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5275000000000001</v>
+        <v>-0.5275</v>
       </c>
       <c r="N10" t="n">
         <v>12.37125</v>
@@ -1899,7 +1899,7 @@
         <v>0.63</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5974999999999999</v>
+        <v>-0.5975</v>
       </c>
       <c r="N12" t="n">
         <v>9.72625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4729</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>279</v>
+      </c>
+      <c r="D75" t="n">
+        <v>222</v>
+      </c>
+      <c r="E75" t="n">
+        <v>57</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-3.42%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>47</v>
+      </c>
+      <c r="J75" t="n">
+        <v>37</v>
+      </c>
+      <c r="K75" t="n">
+        <v>24</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.7375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="X75" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-4.210000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1710686712718408</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-6.999999999999999</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.1600000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.007782101167315147</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
